--- a/Models/Model Outputs/TraitModels_Formatted.xlsx
+++ b/Models/Model Outputs/TraitModels_Formatted.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarahjennings/Desktop/MAPS-Phenology-Project/Models/Model Outputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarahjennings/Desktop/MAPS-Phenology-Project REDO/Models/Model Outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344B6D45-51EA-064D-BED7-090DFEE57522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D9C55C-515D-184E-9182-30E4956FD2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="500" windowWidth="26840" windowHeight="15060" xr2:uid="{23DB0BCD-A074-5F44-9464-C3A450BBDB70}"/>
+    <workbookView xWindow="38740" yWindow="1620" windowWidth="26840" windowHeight="15060" xr2:uid="{23DB0BCD-A074-5F44-9464-C3A450BBDB70}"/>
   </bookViews>
   <sheets>
-    <sheet name="traitmodels" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="63">
   <si>
     <t>STI</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Intercept</t>
   </si>
   <si>
-    <t>Body mass (natural log)</t>
-  </si>
-  <si>
     <t>Species temperature index (STI)</t>
   </si>
   <si>
@@ -95,189 +92,9 @@
     <t>Parameter</t>
   </si>
   <si>
-    <t>0.081 ± 0.067</t>
-  </si>
-  <si>
-    <t>-0.173 ± 1.189</t>
-  </si>
-  <si>
-    <t>-3.679 ± 1.285</t>
-  </si>
-  <si>
-    <t>0.121 ± 0.056</t>
-  </si>
-  <si>
-    <t>0.824 ± 0.998</t>
-  </si>
-  <si>
-    <t>-0.749 ± 1.691</t>
-  </si>
-  <si>
-    <t>1.545 ± 1.156</t>
-  </si>
-  <si>
-    <t>0.003 ± 0.014</t>
-  </si>
-  <si>
-    <t>0.598 ± 0.942</t>
-  </si>
-  <si>
-    <t>0.005 ± 0.015</t>
-  </si>
-  <si>
-    <t>1.085 ± 1.013</t>
-  </si>
-  <si>
-    <t>-0.035 ± 1.568</t>
-  </si>
-  <si>
-    <t>-0.003 ± 0.014</t>
-  </si>
-  <si>
-    <t>0.371 ± 0.944</t>
-  </si>
-  <si>
-    <t>-0.427 ± 1.538</t>
-  </si>
-  <si>
-    <t>-0.012 ± 0.014</t>
-  </si>
-  <si>
-    <t>1.078 ± 0.926</t>
-  </si>
-  <si>
-    <t>2.696 ± 3.165</t>
-  </si>
-  <si>
-    <t>-6.972 ± 6.522</t>
-  </si>
-  <si>
-    <t>0.35 ± 1.058</t>
-  </si>
-  <si>
-    <t>3.923 ± 2.793</t>
-  </si>
-  <si>
-    <t>-9.805 ± 5.756</t>
-  </si>
-  <si>
-    <t>0.616 ± 0.934</t>
-  </si>
-  <si>
     <t>Estimate ± Error</t>
   </si>
   <si>
-    <t>-2.800 ± 1.538</t>
-  </si>
-  <si>
-    <t>-0.020 ± 0.054</t>
-  </si>
-  <si>
-    <t>0.427 ± 1.270</t>
-  </si>
-  <si>
-    <t>-0.029 ± 0.060</t>
-  </si>
-  <si>
-    <t>-1.517 ± 1.530</t>
-  </si>
-  <si>
-    <t>-2.340 ± 1.682</t>
-  </si>
-  <si>
-    <t>-1.090 ± 1.564</t>
-  </si>
-  <si>
-    <t>(-4.517, 1.482)</t>
-  </si>
-  <si>
-    <t>(-0.051, 0.213)</t>
-  </si>
-  <si>
-    <t>(-2.504, 2.157)</t>
-  </si>
-  <si>
-    <t>(-6.196, -1.161)</t>
-  </si>
-  <si>
-    <t>(-4.063, 2.564)</t>
-  </si>
-  <si>
-    <t>(-0.145, 0.088)</t>
-  </si>
-  <si>
-    <t>(-2.063, 2.916)</t>
-  </si>
-  <si>
-    <t>(-5.816, 0.215)</t>
-  </si>
-  <si>
-    <t>(-0.126, 0.086)</t>
-  </si>
-  <si>
-    <t>(-4.154, 1.975)</t>
-  </si>
-  <si>
-    <t>(-0.024, 0.031)</t>
-  </si>
-  <si>
-    <t>(-1.248, 2.443)</t>
-  </si>
-  <si>
-    <t>(-5.636, 0.955)</t>
-  </si>
-  <si>
-    <t>(-0.024, 0.034)</t>
-  </si>
-  <si>
-    <t>(-3.108, 3.038)</t>
-  </si>
-  <si>
-    <t>(-1.479, 2.222)</t>
-  </si>
-  <si>
-    <t>(-3.441, 2.587)</t>
-  </si>
-  <si>
-    <t>(-0.038, 0.015)</t>
-  </si>
-  <si>
-    <t>(-0.737, 2.893)</t>
-  </si>
-  <si>
-    <t>(-3.506, 8.899)</t>
-  </si>
-  <si>
-    <t>(-19.754, 5.811)</t>
-  </si>
-  <si>
-    <t>(-1.724, 2.425)</t>
-  </si>
-  <si>
-    <t>(-1.552, 9.397)</t>
-  </si>
-  <si>
-    <t>(-21.087, 1.476)</t>
-  </si>
-  <si>
-    <t>(-1.214, 2.447)</t>
-  </si>
-  <si>
-    <t>(0.010, 0.231)</t>
-  </si>
-  <si>
-    <t>(-1.132, 2.780)</t>
-  </si>
-  <si>
-    <t>(-0.721, 3.810)</t>
-  </si>
-  <si>
-    <t>(-0.900, 3.069)</t>
-  </si>
-  <si>
-    <t>(-0.030, 0.024)</t>
-  </si>
-  <si>
     <t>95% CI</t>
   </si>
   <si>
@@ -285,6 +102,126 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>-1.716 ± 0.797</t>
+  </si>
+  <si>
+    <t>0.068 ± 0.065</t>
+  </si>
+  <si>
+    <t>-2.748 ± 0.729</t>
+  </si>
+  <si>
+    <t>0.132 ± 0.059</t>
+  </si>
+  <si>
+    <t>-0.183 ± 1.139</t>
+  </si>
+  <si>
+    <t>-0.002 ± 0.013</t>
+  </si>
+  <si>
+    <t>-1.175 ± 1.248</t>
+  </si>
+  <si>
+    <t>0.007 ± 0.015</t>
+  </si>
+  <si>
+    <t>0.096 ± 1.161</t>
+  </si>
+  <si>
+    <t>0.001 ± 0.014</t>
+  </si>
+  <si>
+    <t>0.638 ± 1.224</t>
+  </si>
+  <si>
+    <t>-0.008 ± 0.014</t>
+  </si>
+  <si>
+    <t>-0.617 ± 1.227</t>
+  </si>
+  <si>
+    <t>-0.015 ± 0.055</t>
+  </si>
+  <si>
+    <t>-1.428 ± 1.232</t>
+  </si>
+  <si>
+    <t>0.008 ± 0.056</t>
+  </si>
+  <si>
+    <t>2.771 ± 3.436</t>
+  </si>
+  <si>
+    <t>-6.109 ± 6.942</t>
+  </si>
+  <si>
+    <t>3.673 ± 2.945</t>
+  </si>
+  <si>
+    <t>-7.569 ± 5.950</t>
+  </si>
+  <si>
+    <t>(-3.278, -0.155)</t>
+  </si>
+  <si>
+    <t>(-0.059, 0.196)</t>
+  </si>
+  <si>
+    <t>(-4.177, -1.319)</t>
+  </si>
+  <si>
+    <t>(0.015, 0.248)</t>
+  </si>
+  <si>
+    <t>(-2.416, 2.05)</t>
+  </si>
+  <si>
+    <t>(-0.028, 0.025)</t>
+  </si>
+  <si>
+    <t>(-3.622, 1.272)</t>
+  </si>
+  <si>
+    <t>(-0.022, 0.036)</t>
+  </si>
+  <si>
+    <t>(-2.18, 2.372)</t>
+  </si>
+  <si>
+    <t>(-0.026, 0.028)</t>
+  </si>
+  <si>
+    <t>(-1.761, 3.037)</t>
+  </si>
+  <si>
+    <t>(-3.021, 1.788)</t>
+  </si>
+  <si>
+    <t>(-0.124, 0.093)</t>
+  </si>
+  <si>
+    <t>(-3.843, 0.986)</t>
+  </si>
+  <si>
+    <t>(-0.101, 0.117)</t>
+  </si>
+  <si>
+    <t>(-3.963, 9.506)</t>
+  </si>
+  <si>
+    <t>(-19.715, 7.497)</t>
+  </si>
+  <si>
+    <t>(-2.099, 9.446)</t>
+  </si>
+  <si>
+    <t>(-0.036, 0.020)</t>
+  </si>
+  <si>
+    <t>(-19.230, 4.092)</t>
   </si>
 </sst>
 </file>
@@ -440,7 +377,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -618,6 +555,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -810,7 +753,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -820,17 +763,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="19" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -839,7 +801,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1219,8 +1184,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858B1A30-2F2E-7A45-9993-5A53E0CED3B7}">
-  <dimension ref="A1:H35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5713941-9D75-824E-A9A4-E10515220303}">
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" customWidth="1"/>
@@ -1244,665 +1209,504 @@
         <v>5</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="21" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="13">
+      <c r="E2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="21">
         <v>0</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="21">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="17">
+        <v>0</v>
+      </c>
+      <c r="H4" s="17">
         <v>20</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+    </row>
+    <row r="6" spans="1:8" ht="4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="19">
+        <v>0</v>
+      </c>
+      <c r="H7" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="10">
+      <c r="E9" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H9" s="19">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-    </row>
-    <row r="8" spans="1:8" ht="4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="10" t="s">
+      <c r="E10" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+    </row>
+    <row r="11" spans="1:8" ht="4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>11</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="10">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10" t="s">
-        <v>12</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="E12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="17">
+        <v>0</v>
+      </c>
+      <c r="H12" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="17">
+        <v>0</v>
+      </c>
+      <c r="H14" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+    </row>
+    <row r="16" spans="1:8" ht="4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="19">
+        <v>0</v>
+      </c>
+      <c r="H17" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" spans="1:8" ht="4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G22" s="17">
         <v>0</v>
       </c>
-      <c r="H12" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="H22" s="17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="15" spans="1:8" ht="4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="E24" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G24" s="17">
         <v>0</v>
       </c>
-      <c r="H16" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="5" t="s">
+      <c r="H24" s="17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="10">
-        <v>0</v>
-      </c>
-      <c r="H19" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" ht="4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" s="10">
-        <v>0</v>
-      </c>
-      <c r="H23" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="10">
-        <v>0</v>
-      </c>
-      <c r="H26" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-    </row>
-    <row r="29" spans="1:8" ht="4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" s="10">
-        <v>0</v>
-      </c>
-      <c r="H30" s="10">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G33" s="10">
-        <v>0</v>
-      </c>
-      <c r="H33" s="10">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="H26:H28"/>
-    <mergeCell ref="H30:H32"/>
-    <mergeCell ref="H33:H35"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="G33:G35"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="H12:H14"/>
-    <mergeCell ref="H16:H18"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="G12:G14"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="B30:B35"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="C12:C14"/>
+  <mergeCells count="39">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A12:A15"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>